--- a/Cardiologie/Excel/cardio_10.xlsx
+++ b/Cardiologie/Excel/cardio_10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moito\Desktop\Sérieux\Projet\Site web\Cardiologie\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E2420E-E85C-479A-96FA-47D81A6E15DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E0D9C5A-5AD8-4C55-9151-8AE8182F9A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="239">
   <si>
     <t>La dissection de l'aorte se caractérise par une déchirure transversale de la paroi aortique.</t>
   </si>
@@ -392,6 +392,351 @@
   </si>
   <si>
     <t>image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La dissection se caractérise par une déchirure et un clivage longitudinal de la paroi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">On parle de dissection aiguë si le diagnostic est posé endéans les 14 jours </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le type A intéresse l'aorte ascendante, quelle que soit son extension vers l'aval </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le rapport hommes/femmes est de 5 pour 1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le pic d'incidence pour le type A se situe entre 50 et 60 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'hypertension artérielle est citée comme un facteur prédisposant majeur </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marfan et Ehlers-Danlos sont des maladies du tissu conjonctif prédisposantes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La consommation de cocaïne est un facteur de risque répertorié </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La découverte fortuite par tomodensitométrie (CT) est mentionnée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle permet de visualiser la vraie et la fausse lumière, ainsi que le voile intimal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le type B sans complication bénéficie initialement d'un traitement médical (HTA) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La mortalité sans chirurgie pour le type A est de 55 % (25 % avec traitement) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette complication (ischémie ou thrombose des branches) survient à la phase aiguë </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'évolution anévrismale est citée comme une complication de la phase chronique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il est indiqué pour les dissections chroniques avec dilatation anévrismale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La douleur peut être secondairement migrante vers l'abdomen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'ECG est utilisé pour le diagnostic différentiel de la douleur thoracique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document ne précise pas que l'externe est plus précise que la transoesophagienne </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette méthode (fenestration) est citée pour le traitement des types B aigus compliqués </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement médical vise à contrôler la douleur et la tension artérielle (beta-bloquants) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est un souffle d'insuffisance aortique (et non mitrale) qui peut apparaître </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le rapport est de 5 hommes pour 1 femme </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est favorisée par la dégénérescence physiologique de la média </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le type B correspond à toutes les dissections n'intéressant pas l'aorte ascendante </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le pic d'incidence pour le type A est de 50-60 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'exercice isométrique intense est un facteur de risque cité </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La rupture de l'adventice est effectivement une complication de la phase aiguë </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement du type B aigu est médical, sauf en cas de complications (chirurgie/endo) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toute dissection de type A aigu est une grande urgence chirurgicale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La douleur est d'abord thoracique haute puis migre vers le dos ou les lombaires </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'infarctus myocardique est listé comme un signe d'ischémie possible </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'examen clinique mentionne au contraire une asymétrie des pouls </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La fenestration est une méthode citée pour le traitement du type B aigu compliqué </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'hémopéritoine est une présentation clinique possible (rupture intrapéritonéale) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'ischémie myocardique est une complication possible par hypoperfusion des branches </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le type A (grande urgence chirurgicale) est plus grave que le type B </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette complication est citée pour la phase aiguë </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'accident vasculaire cérébral est cité parmi les signes d'ischémie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'ischémie mésentérique est listée parmi les signes d'ischémie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'hémorragie méningée est possible en cas de dissection de l'artère vertébrale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Rx thorax peut montrer un élargissement de la silhouette aortique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La fenestration (communication vrai/faux) est utilisée pour les types B compliqués </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'IRM montre effectivement un contraste spontané entre les deux chenaux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'ischémie aiguë d'un membre est listée comme une complication possible </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement est indiqué pour les formes chroniques si le diamètre atteint un certain seuil </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les hommes sont 5 fois plus prédisposés que les femmes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le type B affecte toutes les parties de l'aorte SAUF l'aorte ascendante </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle permet de visualiser la vraie lumière, la fausse lumière et le voile intimal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La mortalité du type A (25-55 %) est supérieure à celle du type B (10 %) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le pic d’incidence du type B se situe effectivement entre 60 et 70 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces maladies de la média favorisent le clivage longitudinal de la paroi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'examen clinique peut révéler un souffle diastolique d’insuffisance aortique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est la méthode de traitement chirurgical de référence pour ce type </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La fenestration est une méthode de traitement endovasculaire citée pour le type B aigu avec ischémie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La déchirure survient le plus souvent entre la partie externe de la média et l’adventice </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte définit la dissection comme une déchirure et un clivage longitudinal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La fausse lumière est le deuxième chenal créé, le plus souvent entre média externe et adventice </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le pic d’incidence pour le type A se situe effectivement entre 50 et 60 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est la définition temporelle utilisée pour la forme chronique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C’est la bicuspidie aortique (anomalie congénitale) qui est un facteur prédisposant </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La fin de la grossesse est effectivement listée comme un facteur prédisposant </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La canulation et le traumatisme thoracique fermé (pas ouvert) sont des facteurs de risque </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle peut s'étendre vers l'aval ou vers l'amont (dissection rétrograde) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La déchirure est effectivement le plus souvent due à une poussée d’hypertension artérielle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document mentionne une variabilité des flux à travers le vrai et le faux chenal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'insuffisance valvulaire aortique est une complication de la phase aiguë </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'hypoperfusion des branches peut au contraire conduire à une ischémie viscérale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La douleur est d'emblée maximale et spontanée (pas progressive) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'insuffisance valvulaire aortique aiguë induit effectivement une dyspnée soudaine </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'examen clinique mentionne la présence d'une hypertension artérielle sans préciser de grade </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’asymétrie des pouls est un signe clinique caractéristique mentionné </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte cite l’hémothorax gauche (pas droit), la tamponnade, l'hémopéritoine et le choc </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’ischémie de l’artère d’Adamkiewicz peut entraîner une paraplégie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La mortalité du type B est effectivement de 10 % dans le premier mois </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces chiffres de mortalité (avec et sans chirurgie) sont confirmés pour le type A </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Rx thorax peut au contraire montrer un élargissement de la silhouette aortique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le scanner (CT) nécessite une injection de contraste pour visualiser les deux lumières </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est demandée uniquement dans le cadre d'un bilan préopératoire pour traitement endoluminal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'imagerie permet au contraire de visualiser la vraie et la fausse lumière </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est la fine paroi (clivage de la média) qui sépare la vraie de la fausse lumière </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’échographie trans-oesophagienne (pas transthoracique) permet de visualiser ces éléments </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement médical initial prévoit une surveillance en Unité de Soins Intensifs (U.S.I) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">On utilise un traitement par bêta-bloquant i.v. (le vérapamil n'est pas cité) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'objectif est une TA systolique &lt; 120 mmHg et une TA moyenne de 80 mmHg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement comprend des bêta-bloquants ; la morphine (douleur) n'est pas spécifiée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le type B est traité si rupture, ischémie, douleur persistante ou HTA incontrôlable </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La fenestration consiste à créer une communication entre vrai et faux chenal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La revascularisation par pontage est une méthode citée pour le type B aigu avec ischémie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'endoprothèse sert au contraire à fermer la brèche intimale pour exclure la fausse lumière </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le diamètre opératoire pour l'aorte thoracique descendante est de ≥ 60 mm (pas 55) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le seuil d'intervention est réduit en cas de maladie du tissu conjonctif ou bicuspidie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le diamètre opératoire pour l'aorte abdominale est de ≥ 60 mm (pas 65) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement est indiqué pour l'aorte thoracique descendante si le diamètre ≥ 60 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement chirurgical est indiqué pour l'aorte ascendante si le diamètre ≥ 55 mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Après la 2ème année, la surveillance devient effectivement annuelle (1x/an) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document prévoit une surveillance tous les 6 mois durant la 2ème année (soit 2x/an) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte indique une surveillance à 3 mois lors de la 1ère année (soit 4x/an si on projette) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’ulcère se situe au niveau de l’aorte thoracique (et non abdominale) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'ulcère entraîne effectivement la rupture de la limitante élastique interne </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'extension peut causer un hématome de paroi, un faux-anévrisme, un hémomédiastin ou un hémothorax </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La présentation clinique typique est une douleur thoracique (et non abdominale) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’ulcère touche effectivement le patient âgé et athéromateux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le scanner ou la RMN permettent de visualiser le cratère ulcéreux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement chirurgical ou endovasculaire est indiqué si le diamètre dépasse ce seuil </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement est effectivement chirurgical pour l'aorte ascendante </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La chirurgie est indiquée si la douleur persiste ou en cas d'instabilité </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La douleur persistante est une indication de traitement chirurgical pour l'aorte descendante </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’instabilité hémodynamique impose un traitement chirurgical pour l'aorte descendante </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'expansion de l'hémothorax est une indication chirurgicale citée pour l'aorte descendante </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’ulcère se développe au contraire au niveau d’une plaque athéromateuse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La surveillance se poursuit la 2ème année, puis annuellement </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'intervention est envisagée pour un diamètre plus petit en cas de maladie du tissu conjonctif </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La présentation clinique mentionnée est la douleur thoracique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte mentionne l'hémothorax et l'hémomédiastin, mais pas l'hémopéritoine pour les ulcères </t>
+  </si>
+  <si>
+    <t>Page</t>
   </si>
 </sst>
 </file>
@@ -739,16 +1084,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:H118"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="164.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="8.28515625" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>117</v>
       </c>
@@ -762,16 +1108,19 @@
         <v>120</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -781,8 +1130,14 @@
       <c r="C2" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -792,8 +1147,14 @@
       <c r="C3" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -803,8 +1164,14 @@
       <c r="C4" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -814,8 +1181,14 @@
       <c r="C5" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -825,8 +1198,14 @@
       <c r="C6" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -836,8 +1215,14 @@
       <c r="C7" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -847,8 +1232,14 @@
       <c r="C8" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>130</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -858,8 +1249,14 @@
       <c r="C9" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -869,8 +1266,14 @@
       <c r="C10" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>132</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -880,8 +1283,14 @@
       <c r="C11" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -891,8 +1300,14 @@
       <c r="C12" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E12" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -902,8 +1317,14 @@
       <c r="C13" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>135</v>
+      </c>
+      <c r="E13" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -913,8 +1334,14 @@
       <c r="C14" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -924,8 +1351,14 @@
       <c r="C15" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>137</v>
+      </c>
+      <c r="E15" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -935,8 +1368,14 @@
       <c r="C16" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>138</v>
+      </c>
+      <c r="E16" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -946,8 +1385,14 @@
       <c r="C17" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>139</v>
+      </c>
+      <c r="E17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -957,8 +1402,14 @@
       <c r="C18" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>140</v>
+      </c>
+      <c r="E18" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -968,8 +1419,14 @@
       <c r="C19" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>141</v>
+      </c>
+      <c r="E19" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -979,8 +1436,14 @@
       <c r="C20" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
+        <v>142</v>
+      </c>
+      <c r="E20" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -990,8 +1453,14 @@
       <c r="C21" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
+        <v>143</v>
+      </c>
+      <c r="E21" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1001,8 +1470,14 @@
       <c r="C22" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>144</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1012,8 +1487,14 @@
       <c r="C23" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>145</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1023,8 +1504,14 @@
       <c r="C24" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>146</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1034,8 +1521,14 @@
       <c r="C25" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>147</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1045,8 +1538,14 @@
       <c r="C26" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26" t="s">
+        <v>148</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1056,8 +1555,14 @@
       <c r="C27" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>149</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1067,8 +1572,14 @@
       <c r="C28" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>150</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1078,8 +1589,14 @@
       <c r="C29" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
+        <v>151</v>
+      </c>
+      <c r="E29" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1089,8 +1606,14 @@
       <c r="C30" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30" t="s">
+        <v>152</v>
+      </c>
+      <c r="E30" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1100,8 +1623,14 @@
       <c r="C31" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>153</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1111,8 +1640,14 @@
       <c r="C32" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>154</v>
+      </c>
+      <c r="E32" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1122,8 +1657,14 @@
       <c r="C33" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>155</v>
+      </c>
+      <c r="E33" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1133,8 +1674,14 @@
       <c r="C34" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
+        <v>156</v>
+      </c>
+      <c r="E34" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1144,8 +1691,14 @@
       <c r="C35" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
+        <v>157</v>
+      </c>
+      <c r="E35" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -1155,8 +1708,14 @@
       <c r="C36" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36" t="s">
+        <v>158</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1166,8 +1725,14 @@
       <c r="C37" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>159</v>
+      </c>
+      <c r="E37" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1177,8 +1742,14 @@
       <c r="C38" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
+        <v>160</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -1188,8 +1759,14 @@
       <c r="C39" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39" t="s">
+        <v>161</v>
+      </c>
+      <c r="E39" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -1199,8 +1776,14 @@
       <c r="C40" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
+        <v>162</v>
+      </c>
+      <c r="E40" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -1208,10 +1791,16 @@
         <v>37</v>
       </c>
       <c r="C41" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D41" t="s">
+        <v>163</v>
+      </c>
+      <c r="E41" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -1221,8 +1810,14 @@
       <c r="C42" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42" t="s">
+        <v>164</v>
+      </c>
+      <c r="E42" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -1232,8 +1827,14 @@
       <c r="C43" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43" t="s">
+        <v>165</v>
+      </c>
+      <c r="E43" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -1243,8 +1844,14 @@
       <c r="C44" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44" t="s">
+        <v>166</v>
+      </c>
+      <c r="E44" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -1254,8 +1861,14 @@
       <c r="C45" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45" t="s">
+        <v>167</v>
+      </c>
+      <c r="E45" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -1265,8 +1878,14 @@
       <c r="C46" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D46" t="s">
+        <v>168</v>
+      </c>
+      <c r="E46" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -1276,8 +1895,14 @@
       <c r="C47" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47" t="s">
+        <v>169</v>
+      </c>
+      <c r="E47" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -1287,8 +1912,14 @@
       <c r="C48" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D48" t="s">
+        <v>170</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -1298,8 +1929,14 @@
       <c r="C49" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D49" t="s">
+        <v>128</v>
+      </c>
+      <c r="E49" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -1309,8 +1946,14 @@
       <c r="C50" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D50" t="s">
+        <v>171</v>
+      </c>
+      <c r="E50" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -1320,8 +1963,14 @@
       <c r="C51" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D51" t="s">
+        <v>172</v>
+      </c>
+      <c r="E51" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -1331,8 +1980,14 @@
       <c r="C52" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D52" t="s">
+        <v>173</v>
+      </c>
+      <c r="E52" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -1342,8 +1997,14 @@
       <c r="C53" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D53" t="s">
+        <v>174</v>
+      </c>
+      <c r="E53" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -1353,8 +2014,14 @@
       <c r="C54" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D54" t="s">
+        <v>175</v>
+      </c>
+      <c r="E54" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -1364,8 +2031,14 @@
       <c r="C55" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D55" t="s">
+        <v>176</v>
+      </c>
+      <c r="E55" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -1375,8 +2048,14 @@
       <c r="C56" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D56" t="s">
+        <v>177</v>
+      </c>
+      <c r="E56" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -1386,8 +2065,14 @@
       <c r="C57" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D57" t="s">
+        <v>178</v>
+      </c>
+      <c r="E57" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -1397,8 +2082,14 @@
       <c r="C58" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D58" t="s">
+        <v>179</v>
+      </c>
+      <c r="E58" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -1408,8 +2099,14 @@
       <c r="C59" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D59" t="s">
+        <v>125</v>
+      </c>
+      <c r="E59" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -1419,8 +2116,14 @@
       <c r="C60" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D60" t="s">
+        <v>180</v>
+      </c>
+      <c r="E60" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -1430,8 +2133,14 @@
       <c r="C61" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D61" t="s">
+        <v>181</v>
+      </c>
+      <c r="E61" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -1441,8 +2150,14 @@
       <c r="C62" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D62" t="s">
+        <v>182</v>
+      </c>
+      <c r="E62" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -1452,8 +2167,14 @@
       <c r="C63" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D63" t="s">
+        <v>183</v>
+      </c>
+      <c r="E63" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -1463,8 +2184,14 @@
       <c r="C64" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D64" t="s">
+        <v>184</v>
+      </c>
+      <c r="E64" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -1474,8 +2201,14 @@
       <c r="C65" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D65" t="s">
+        <v>185</v>
+      </c>
+      <c r="E65" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -1485,8 +2218,14 @@
       <c r="C66" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D66" t="s">
+        <v>186</v>
+      </c>
+      <c r="E66" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -1496,8 +2235,14 @@
       <c r="C67" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D67" t="s">
+        <v>187</v>
+      </c>
+      <c r="E67" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -1507,8 +2252,14 @@
       <c r="C68" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D68" t="s">
+        <v>188</v>
+      </c>
+      <c r="E68" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -1518,8 +2269,14 @@
       <c r="C69" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D69" t="s">
+        <v>189</v>
+      </c>
+      <c r="E69" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -1529,8 +2286,14 @@
       <c r="C70" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D70" t="s">
+        <v>190</v>
+      </c>
+      <c r="E70" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -1540,8 +2303,14 @@
       <c r="C71" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D71" t="s">
+        <v>191</v>
+      </c>
+      <c r="E71" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -1551,8 +2320,14 @@
       <c r="C72" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D72" t="s">
+        <v>192</v>
+      </c>
+      <c r="E72" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -1562,8 +2337,14 @@
       <c r="C73" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D73" t="s">
+        <v>193</v>
+      </c>
+      <c r="E73" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -1573,8 +2354,14 @@
       <c r="C74" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D74" t="s">
+        <v>194</v>
+      </c>
+      <c r="E74" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -1584,8 +2371,14 @@
       <c r="C75" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D75" t="s">
+        <v>195</v>
+      </c>
+      <c r="E75" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -1595,8 +2388,14 @@
       <c r="C76" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D76" t="s">
+        <v>196</v>
+      </c>
+      <c r="E76" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -1606,8 +2405,14 @@
       <c r="C77" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D77" t="s">
+        <v>197</v>
+      </c>
+      <c r="E77" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -1617,8 +2422,14 @@
       <c r="C78" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D78" t="s">
+        <v>198</v>
+      </c>
+      <c r="E78" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -1628,8 +2439,14 @@
       <c r="C79" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D79" t="s">
+        <v>199</v>
+      </c>
+      <c r="E79" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -1639,8 +2456,14 @@
       <c r="C80" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D80" t="s">
+        <v>200</v>
+      </c>
+      <c r="E80" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -1650,8 +2473,14 @@
       <c r="C81" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D81" t="s">
+        <v>201</v>
+      </c>
+      <c r="E81" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -1661,8 +2490,14 @@
       <c r="C82" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D82" t="s">
+        <v>202</v>
+      </c>
+      <c r="E82" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -1672,8 +2507,14 @@
       <c r="C83" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D83" t="s">
+        <v>203</v>
+      </c>
+      <c r="E83" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -1683,8 +2524,14 @@
       <c r="C84" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D84" t="s">
+        <v>204</v>
+      </c>
+      <c r="E84" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -1694,8 +2541,14 @@
       <c r="C85" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D85" t="s">
+        <v>205</v>
+      </c>
+      <c r="E85" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -1705,8 +2558,14 @@
       <c r="C86" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D86" t="s">
+        <v>206</v>
+      </c>
+      <c r="E86" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -1716,8 +2575,14 @@
       <c r="C87" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D87" t="s">
+        <v>207</v>
+      </c>
+      <c r="E87" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -1727,8 +2592,14 @@
       <c r="C88" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D88" t="s">
+        <v>208</v>
+      </c>
+      <c r="E88" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -1738,8 +2609,14 @@
       <c r="C89" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D89" t="s">
+        <v>152</v>
+      </c>
+      <c r="E89" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -1749,8 +2626,14 @@
       <c r="C90" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D90" t="s">
+        <v>209</v>
+      </c>
+      <c r="E90" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -1760,8 +2643,14 @@
       <c r="C91" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D91" t="s">
+        <v>210</v>
+      </c>
+      <c r="E91" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -1771,8 +2660,14 @@
       <c r="C92" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D92" t="s">
+        <v>211</v>
+      </c>
+      <c r="E92" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -1782,8 +2677,14 @@
       <c r="C93" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D93" t="s">
+        <v>212</v>
+      </c>
+      <c r="E93" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -1793,8 +2694,14 @@
       <c r="C94" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D94" t="s">
+        <v>213</v>
+      </c>
+      <c r="E94" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -1804,8 +2711,14 @@
       <c r="C95" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D95" t="s">
+        <v>214</v>
+      </c>
+      <c r="E95" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -1815,8 +2728,14 @@
       <c r="C96" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D96" t="s">
+        <v>215</v>
+      </c>
+      <c r="E96" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -1826,8 +2745,14 @@
       <c r="C97" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D97" t="s">
+        <v>216</v>
+      </c>
+      <c r="E97" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -1837,8 +2762,14 @@
       <c r="C98" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D98" t="s">
+        <v>217</v>
+      </c>
+      <c r="E98" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -1848,8 +2779,14 @@
       <c r="C99" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D99" t="s">
+        <v>218</v>
+      </c>
+      <c r="E99" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -1859,8 +2796,14 @@
       <c r="C100" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D100" t="s">
+        <v>219</v>
+      </c>
+      <c r="E100" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -1870,8 +2813,14 @@
       <c r="C101" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D101" t="s">
+        <v>220</v>
+      </c>
+      <c r="E101" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -1881,8 +2830,14 @@
       <c r="C102" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D102" t="s">
+        <v>221</v>
+      </c>
+      <c r="E102" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -1892,8 +2847,14 @@
       <c r="C103" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D103" t="s">
+        <v>222</v>
+      </c>
+      <c r="E103" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -1903,8 +2864,14 @@
       <c r="C104" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D104" t="s">
+        <v>223</v>
+      </c>
+      <c r="E104" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -1914,8 +2881,14 @@
       <c r="C105" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D105" t="s">
+        <v>224</v>
+      </c>
+      <c r="E105" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>105</v>
       </c>
@@ -1925,8 +2898,14 @@
       <c r="C106" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D106" t="s">
+        <v>225</v>
+      </c>
+      <c r="E106" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>106</v>
       </c>
@@ -1936,8 +2915,14 @@
       <c r="C107" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D107" t="s">
+        <v>226</v>
+      </c>
+      <c r="E107" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>107</v>
       </c>
@@ -1947,8 +2932,14 @@
       <c r="C108" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D108" t="s">
+        <v>227</v>
+      </c>
+      <c r="E108" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>108</v>
       </c>
@@ -1958,8 +2949,14 @@
       <c r="C109" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D109" t="s">
+        <v>228</v>
+      </c>
+      <c r="E109" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>109</v>
       </c>
@@ -1969,8 +2966,14 @@
       <c r="C110" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D110" t="s">
+        <v>229</v>
+      </c>
+      <c r="E110" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>110</v>
       </c>
@@ -1980,8 +2983,14 @@
       <c r="C111" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D111" t="s">
+        <v>230</v>
+      </c>
+      <c r="E111" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>111</v>
       </c>
@@ -1991,8 +3000,14 @@
       <c r="C112" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D112" t="s">
+        <v>231</v>
+      </c>
+      <c r="E112" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>112</v>
       </c>
@@ -2002,8 +3017,14 @@
       <c r="C113" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D113" t="s">
+        <v>232</v>
+      </c>
+      <c r="E113" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>113</v>
       </c>
@@ -2013,8 +3034,14 @@
       <c r="C114" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D114" t="s">
+        <v>233</v>
+      </c>
+      <c r="E114" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>114</v>
       </c>
@@ -2024,8 +3051,14 @@
       <c r="C115" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D115" t="s">
+        <v>234</v>
+      </c>
+      <c r="E115" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>115</v>
       </c>
@@ -2035,8 +3068,14 @@
       <c r="C116" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D116" t="s">
+        <v>235</v>
+      </c>
+      <c r="E116" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>116</v>
       </c>
@@ -2046,8 +3085,14 @@
       <c r="C117" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D117" t="s">
+        <v>236</v>
+      </c>
+      <c r="E117" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>117</v>
       </c>
@@ -2056,6 +3101,12 @@
       </c>
       <c r="C118" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="D118" t="s">
+        <v>237</v>
+      </c>
+      <c r="E118" s="1">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
